--- a/output/pdf_financials_xlsx/SGE.xlsx
+++ b/output/pdf_financials_xlsx/SGE.xlsx
@@ -1379,7 +1379,7 @@
         <v>0.517885</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.168782</v>
+        <v>-3.437192</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>2.56917</v>
@@ -1621,7 +1621,7 @@
         <v>-1.440513</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.634205</v>
+        <v>-1.634205</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-3.433666</v>
@@ -1795,7 +1795,7 @@
         <v>-1.440513</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.634205</v>
+        <v>-1.634205</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-3.433666</v>
@@ -1969,7 +1969,7 @@
         <v>5.335233</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5.271629</v>
+        <v>-5.271629</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>5.282563</v>
@@ -2275,7 +2275,7 @@
         <v>-26.44431826421391</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>9.361243314566329</v>
+        <v>190.6387566854337</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>6151.490482461391</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>77.9220314786497</v>
+        <v>-77.9220314786497</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>-164.200047055493</v>
@@ -6221,7 +6221,7 @@
         <v>-1.440513</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>1.634205</v>
+        <v>-1.634205</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-3.433666</v>
@@ -40441,7 +40441,7 @@
         <v>-1.440513</v>
       </c>
       <c r="I326" s="5" t="n">
-        <v>1.634205</v>
+        <v>-1.634205</v>
       </c>
       <c r="J326" s="5" t="n">
         <v>-3.433666</v>
@@ -40455,7 +40455,7 @@
         <v>-0.89373</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>4.282372</v>
+        <v>-4.282372</v>
       </c>
       <c r="N326" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>-1.729</v>
       </c>
       <c r="T326" s="5" t="n">
-        <v>0.644</v>
+        <v>-0.644</v>
       </c>
       <c r="U326" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SGE.xlsx
+++ b/output/pdf_financials_xlsx/SGE.xlsx
@@ -954,46 +954,46 @@
         <v>0.579472</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.120029</v>
+        <v>0.266587</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.10464</v>
+        <v>0.294244</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.1115</v>
+        <v>0.271422</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.096178</v>
+        <v>0.414831</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.11684</v>
+        <v>0.441559</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.11592</v>
+        <v>0.524322</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.11592</v>
+        <v>0.310042</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.11592</v>
+        <v>0.300867</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.11592</v>
+        <v>0.265665</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1.118</v>
+        <v>1.457</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.261</v>
+        <v>0.795</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.248</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.244</v>
+        <v>0.376</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.237</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="11">
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.992591</v>
+        <v>1.802987</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.979648</v>
+        <v>1.819726</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.856091</v>
+        <v>1.447689</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.55165</v>
+        <v>1.357528</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.738</v>
+        <v>0.606</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.705</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="12">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.07757799999999999</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -2039,7 +2039,7 @@
         <v>-1.385066</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.58622</v>
+        <v>2.508642</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>1.366241</v>
@@ -2155,7 +2155,7 @@
         <v>-1.384907</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.58622</v>
+        <v>2.508642</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>1.366241</v>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>131.1463272770791</v>
+        <v>127.2123735618108</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>81.93005391078036</v>
@@ -39271,7 +39271,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -39542,7 +39542,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -40910,7 +40910,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -41421,7 +41421,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -45452,7 +45452,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -47476,7 +47476,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">

--- a/output/pdf_financials_xlsx/SGE.xlsx
+++ b/output/pdf_financials_xlsx/SGE.xlsx
@@ -771,40 +771,40 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.076488</v>
+        <v>0.104488</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.240054</v>
+        <v>0.268054</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.351996</v>
+        <v>0.379996</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.120029</v>
+        <v>0.155029</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.10464</v>
+        <v>0.14664</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1115</v>
+        <v>0.1535</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.096178</v>
+        <v>0.138178</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.11684</v>
+        <v>0.15884</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.11592</v>
+        <v>0.15792</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.11592</v>
+        <v>0.15792</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.11592</v>
+        <v>0.15792</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.11592</v>
+        <v>0.15792</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>1.118</v>
@@ -1385,13 +1385,13 @@
         <v>2.56917</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1.299959</v>
+        <v>-0.00413</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.313335</v>
+        <v>-0.178001</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.240709</v>
+        <v>-1.936861</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0.266959</v>
@@ -1403,10 +1403,10 @@
         <v>0.475494</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-2.254</v>
+        <v>2.725</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>2.725</v>
+        <v>-2.725</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
@@ -2281,13 +2281,13 @@
         <v>6151.490482461391</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-87.21168083006671</v>
+        <v>-0.2770735398794696</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-22.62238766961286</v>
+        <v>-12.85144534628675</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>9.307367509337952</v>
+        <v>74.89157921599863</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>19.53967125858469</v>
@@ -2299,7 +2299,7 @@
         <v>142.8167237340061</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>21.39128784283952</v>
+        <v>25.86125083040713</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-13.38934748427673</v>
@@ -6221,7 +6221,7 @@
         <v>-1.440513</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-1.634205</v>
+        <v>1.634205</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-3.433666</v>
@@ -7137,55 +7137,55 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>11.111563</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>2.51577</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.984897</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>2.348534</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.910465</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>1.119758</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>7.658308</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>2.037497</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>3.038194</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>2.479012</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>3.710211</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>9.095615</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>7.101</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>4.175</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>6.754</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>5.266</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>2.496</v>
       </c>
     </row>
     <row r="116">
@@ -21236,7 +21236,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -22153,7 +22157,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -23810,7 +23818,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -25097,7 +25109,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -26839,7 +26855,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -27734,7 +27754,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -29037,7 +29061,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -32746,7 +32774,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -34463,7 +34495,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -35073,7 +35109,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E272" s="5" t="n">
         <v>11.111563</v>
       </c>
@@ -41724,7 +41764,11 @@
           <t>Deferred income tax recovery (expense) 10</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -41823,7 +41867,11 @@
           <t>Net income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -42494,7 +42542,11 @@
           <t>Director fees 6</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -43090,7 +43142,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
@@ -44460,7 +44516,11 @@
           <t>Deferred income tax recovery (expense) 9</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -45755,7 +45815,11 @@
           <t>Income tax recovery 9</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -47167,7 +47231,11 @@
           <t>Director fees 8</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -47680,7 +47748,11 @@
           <t>Income tax recovery 11</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -48280,7 +48352,11 @@
           <t>Director fees 9</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -48676,7 +48752,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -48775,7 +48855,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -50278,7 +50362,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -52080,7 +52168,11 @@
           <t>Director fees 10</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E443" t="inlineStr">
         <is>
           <t>-</t>
@@ -54181,7 +54273,11 @@
           <t>Director fees (Note 9)</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
@@ -55799,7 +55895,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E480" s="5" t="n">
         <v>0.028</v>
       </c>
